--- a/excel-files/MANILA/CECILIO APOSTOL ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/MANILA/CECILIO APOSTOL ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6533A582-57B7-40C4-9028-3A7069DBE78A}"/>
+  <xr:revisionPtr revIDLastSave="281" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFBA7CF9-B047-4146-B922-764293AD61C3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3630,7 +3630,9 @@
         <v>152</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1">
+        <v>2025</v>
+      </c>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
@@ -3945,7 +3947,7 @@
         <v>386</v>
       </c>
       <c r="E22" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>16</v>
@@ -5519,12 +5521,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{2C7657B9-60EB-4532-B02D-CD2C044C7EF0}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5536,7 +5541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5761,7 +5766,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5830,7 +5835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5899,7 +5904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5968,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6037,7 +6042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6106,7 +6111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6175,7 +6180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6244,7 +6249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6313,7 +6318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6326,7 +6331,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6395,7 +6400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6464,7 +6469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6533,7 +6538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6602,7 +6607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6671,7 +6676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6740,7 +6745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6809,7 +6814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6878,7 +6883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6892,7 +6897,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6961,7 +6966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7030,7 +7035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7099,7 +7104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7168,7 +7173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7237,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7306,7 +7311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7375,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7444,7 +7449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7513,7 +7518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7527,7 +7532,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7596,7 +7601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7665,7 +7670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7734,7 +7739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7803,7 +7808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7872,7 +7877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7941,7 +7946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8010,7 +8015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8079,7 +8084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8231,7 +8236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8300,7 +8305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8369,7 +8374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8438,7 +8443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8507,7 +8512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8576,7 +8581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8645,7 +8650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8714,7 +8719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8783,7 +8788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8797,7 +8802,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8866,7 +8871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8935,7 +8940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9004,7 +9009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9073,7 +9078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9142,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9211,7 +9216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9280,7 +9285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9349,7 +9354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9501,7 +9506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9570,7 +9575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9639,7 +9644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9708,7 +9713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9777,7 +9782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9846,7 +9851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9915,7 +9920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9984,7 +9989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10053,7 +10058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10067,7 +10072,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10136,7 +10141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10205,7 +10210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10274,7 +10279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10343,7 +10348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10412,7 +10417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10481,7 +10486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10550,7 +10555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10619,7 +10624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10688,7 +10693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10702,7 +10707,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10771,7 +10776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10840,7 +10845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10909,7 +10914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10978,7 +10983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11047,7 +11052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11116,7 +11121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11185,7 +11190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11254,7 +11259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11406,7 +11411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11475,7 +11480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11544,7 +11549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11613,7 +11618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11682,7 +11687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11751,7 +11756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11820,7 +11825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11889,7 +11894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12041,7 +12046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>25</v>
       </c>
@@ -12110,7 +12115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>25</v>
       </c>
@@ -12179,7 +12184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>25</v>
       </c>
@@ -12248,7 +12253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>25</v>
       </c>
@@ -12317,7 +12322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>25</v>
       </c>
@@ -12386,7 +12391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>25</v>
       </c>
@@ -12455,7 +12460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>25</v>
       </c>
@@ -12597,7 +12602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12659,7 +12664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12721,7 +12726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12783,7 +12788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12845,7 +12850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12907,7 +12912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12969,7 +12974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13031,7 +13036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13093,7 +13098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13155,7 +13160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13217,7 +13222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13279,7 +13284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13341,7 +13346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13403,7 +13408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13465,13 +13470,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="1"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
@@ -13486,7 +13491,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13498,7 +13503,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13513,7 +13518,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13524,190 +13529,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 H33:I41 H43:I51 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 H103:I110 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127 K6:L12 K33:L41 K23:L31 K14:L21 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 Q113:Q126 R113:R127 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W63:X71 W73:X81 W83:X91 W93:X101 W103:X110 W112:X127 D5:F12" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13717,15 +13542,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 F5:F12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X103:X110 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L33:L41 L23:L31 L5:L12 L14:L21 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101" xr:uid="{76CF397E-9C4D-467A-8505-3B5800265A86}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R63:R71" xr:uid="{9CB83040-D6D5-4B1D-8587-45623735F9C3}">
+      <formula1>"2024,20252026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13886,7 +13717,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="38.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14715,7 +14546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14853,7 +14684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -22190,12 +22021,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{03D964A2-BB47-44ED-9B6B-BF016723864E}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
